--- a/checklist_forms/033_grievance_handling_checklist_form--checklist_forms.xlsx
+++ b/checklist_forms/033_grievance_handling_checklist_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'grievance_type',_'label':_'grievance_type'}</t>
+          <t>grievance_type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Grievance Type', 'label': 'grievance_type'}</t>
+          <t>grievance type</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'grievance_description',_'label':_'grievance_description'}</t>
+          <t>grievance_description</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'grievance_description', 'label': 'grievance_description'}</t>
+          <t>grievance description</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'new',_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'new', 'label': 'new'}</t>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'ongoing',_'label':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'ongoing', 'label': 'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'closed',_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'closed', 'label': 'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'category_1',_'label':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Category 1', 'label': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'category_2',_'label':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Category 2', 'label': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'category_3',_'label':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Category 3', 'label': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'resolved',_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'resolved', 'label': 'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'unresolved',_'label':_'unresolved'}</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'unresolved', 'label': 'unresolved'}</t>
+          <t>unresolved</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
